--- a/psychologist_forms/018_psychological_reliability_assessment--psychologist_forms.xlsx
+++ b/psychologist_forms/018_psychological_reliability_assessment--psychologist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -722,40 +722,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Emergency Contact</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>emergency_contact</t>
+          <t>emergency_phone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Emergency Contact</t>
+          <t>Emergency Phone</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,366 +768,67 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>emergency_phone</t>
+          <t>client_agreed_to_terms</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Emergency Phone</t>
+          <t>Client Agreed To Terms</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>emergency_relationship</t>
+          <t>informed_consents</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emergency Relationship</t>
+          <t>Informed Consents</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>client_agreed_to_terms</t>
+          <t>emergency_phone_list</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Client Agreed To Terms</t>
+          <t>Emergency Phone Numbers</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>informed_consents</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Informed Consents</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>emergency_phone_1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Emergency Phone</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>emergency_phone_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Emergency Phone</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>emergency_phone_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Emergency Phone</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>emergency_phone_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Emergency Phone</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>emergency_phone_5</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Emergency Phone</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>emergency_phone_6</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Emergency Phone</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>emergency_phone_7</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Emergency Phone</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>emergency_phone_8</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Emergency Phone</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>emergency_phone_9</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Emergency Phone</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>emergency_phone_10</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Emergency Phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>emergency_phone_11</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Emergency Phone</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>emergency_phone_11</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Emergency Phone</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1148,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1177,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1194,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'athlete'}</t>
+          <t>athlete</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Athlete'}</t>
+          <t>Athlete</t>
         </is>
       </c>
     </row>
@@ -1211,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'artist'}</t>
+          <t>artist</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Artist'}</t>
+          <t>Artist</t>
         </is>
       </c>
     </row>
@@ -1228,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'business_owner'}</t>
+          <t>business_owner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Business Owner'}</t>
+          <t>Business Owner</t>
         </is>
       </c>
     </row>
@@ -1245,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1262,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1279,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1296,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'self'}</t>
+          <t>self</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Self'}</t>
+          <t>Self</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
